--- a/static/standards-correlations/Vermont_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Vermont_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$32</definedName>
@@ -550,10 +550,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Vermont has no CS standards; ISTE is the adopted framework</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Vermont has no CS standards; ISTE is the adopted framework</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -587,7 +588,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -640,7 +641,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Discovery Systems covers goal setting, ranking goals, and timeline feedback. Labs prompt reflection but do not formalize personal learning-goal setting.</t>
+          <t>Introductory Systems covers goal setting, ranking goals, and timeline feedback. Labs prompt reflection but do not formalize personal learning-goal setting.</t>
         </is>
       </c>
     </row>
@@ -777,7 +778,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>PreLabs cover the controller and the toolchain directly. Discovery Systems adds kit inventory, what qualifies as a robot, and the hardware/software split.</t>
+          <t>PreLabs cover the controller and the toolchain directly. Introductory Systems adds kit inventory, what qualifies as a robot, and the hardware/software split.</t>
         </is>
       </c>
     </row>
@@ -949,7 +950,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 10 covers what counts as personal information, how it is sought, and how to protect it.</t>
+          <t>Introductory Systems 10 covers what counts as personal information, how it is sought, and how to protect it.</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1181,7 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems teaches define-brainstorm-build-test-improve explicitly; labs apply decomposition and top-down planning.</t>
+          <t>Introductory Systems teaches define-brainstorm-build-test-improve explicitly; labs apply decomposition and top-down planning.</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1510,7 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>The entire curriculum is autonomous robotics. Discovery Systems 3 addresses autonomy levels directly.</t>
+          <t>The entire curriculum is autonomous robotics. Introductory Systems 3 addresses autonomy levels directly.</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1819,7 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 13 and 14 teach roles, goal ranking, and timelines. Botball team structure reinforces this throughout.</t>
+          <t>Introductory Systems 13 and 14 teach roles, goal ranking, and timelines. Botball team structure reinforces this throughout.</t>
         </is>
       </c>
     </row>
@@ -1899,6 +1900,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -1943,7 +1945,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1957,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2079,6 +2081,8 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
@@ -2107,7 +2111,7 @@
 STANDARD STATEMENTS ARE PARAPHRASED, not reproduced verbatim, for copyright reasons. Official codes and indicator names are retained as factual identifiers. ISTE Standards for Students (c) ISTE.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.
 RESULT: 22 Full, 6 Partial, 0 BLANK of 28. Touched 28 of 28.
 This is the only file in the series with NO blanks, and the reason is structural rather than flattering: ISTE indicators are written as broad dispositions - empowered learner, knowledge constructor, computational thinker - rather than as specific technical content like the CIA triad, ASCII conversion, or API. Broad indicators are easier to evidence. Do NOT present a 28-of-28 result next to a state file scored against technical content standards without saying why the two are not comparable. The same caution already applies to Ohio and South Carolina in this set.
